--- a/Areas/School/study-plan.xlsx
+++ b/Areas/School/study-plan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Academic Planning Guide" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="159">
   <si>
     <t xml:space="preserve">Mathematics Academic Planning Guide</t>
   </si>
@@ -45,6 +45,7 @@
         <color rgb="FF000000"/>
         <rFont val="Century Gothic"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Students who need fewer than 12SH to meet all program requirements in their </t>
     </r>
@@ -55,6 +56,7 @@
         <color rgb="FF000000"/>
         <rFont val="Century Gothic"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">final</t>
     </r>
@@ -64,6 +66,7 @@
         <color rgb="FF000000"/>
         <rFont val="Century Gothic"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> semester qualify for a reduced courseload and will be charged by the tuition.
 Students taking only once class in any summer term  qualify for a reduced coursload. 
@@ -375,63 +378,156 @@
     <t xml:space="preserve">MATH3275</t>
   </si>
   <si>
+    <t xml:space="preserve">MATH 5510 #4 of 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH1365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH ELECTIVE #2 OF 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGW3306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH3081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH3150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH ELECTIVE #1 OF 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH ELECTIVE #3 OF 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQUIRED PHYSICS 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose a lecture &amp; lab from selections on degree audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ND, AD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQUIRED PHYSICS 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPSTONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose from selections on degree audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WI, CE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH CAPSTONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPPER DIVISION ELECTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete general elective at 3000 level or above</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ART2360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH 4565 (or other topology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analysis 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algebra 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATH3000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUPath not met by Major:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRADUATE APRIL 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creative Expression - EI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose from NUpath list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpreting Culture - IC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Societies &amp; Institutions -SI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference &amp; Diversity - DD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethical Reasoning - ER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGW 1111 - WF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Year Writing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGW 3307 (recommended) or 3315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration Experience - EX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typically Coop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">***This is a sample graduation plan and may vary according to course availability. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Electives - if needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting Notes: </t>
+  </si>
+  <si>
     <t xml:space="preserve">PHYS 2303</t>
   </si>
   <si>
-    <t xml:space="preserve">MATH1365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MATH ELECTIVE #2 OF 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MATH ELECTIVE #4 OF 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MATH3081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MATH3150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MATH ELECTIVE #1 OF 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MATH ELECTIVE #3 OF 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQUIRED PHYSICS 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Choose a lecture &amp; lab from selections on degree audit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ND, AD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQUIRED PHYSICS 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPSTONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Choose from selections on degree audit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WI, CE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MATH CAPSTONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UPPER DIVISION ELECTIVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete general elective at 3000 level or above</t>
-  </si>
-  <si>
     <t xml:space="preserve">ENGW3315</t>
   </si>
   <si>
@@ -442,84 +538,6 @@
   </si>
   <si>
     <t xml:space="preserve">PHYS2372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MATH3000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUPath not met by Major:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRADUATE APRIL 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creative Expression - EI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Choose from NUpath list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interpreting Culture - IC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-2028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Societies &amp; Institutions -SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference &amp; Diversity - DD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethical Reasoning - ER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENGW 1111 - WF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Year Writing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENGW 3307 (recommended) or 3315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration Experience - EX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Typically Coop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">***This is a sample graduation plan and may vary according to course availability. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">General Electives - if needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meeting Notes: </t>
   </si>
 </sst>
 </file>
@@ -530,12 +548,13 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="000000000"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -553,17 +572,12 @@
       <family val="0"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -571,12 +585,14 @@
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -584,6 +600,7 @@
       <color rgb="FF000000"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -591,19 +608,14 @@
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -611,6 +623,7 @@
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -618,18 +631,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <u val="single"/>
@@ -637,12 +646,14 @@
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -651,6 +662,7 @@
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -658,6 +670,7 @@
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -871,23 +884,23 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="74">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -900,15 +913,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -916,19 +929,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -940,251 +953,247 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1225,7 +1234,7 @@
       <rgbColor rgb="FFE1EEE9"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0070C0"/>
+      <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFD1DDB0"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -1389,7 +1398,7 @@
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1427,7 +1436,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -1497,7 +1506,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>21</v>
       </c>
@@ -1533,7 +1542,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
     </row>
-    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>27</v>
       </c>
@@ -1799,7 +1808,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="15" style="13" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
         <v>49</v>
       </c>
@@ -1887,44 +1896,44 @@
       <c r="H5" s="28"/>
       <c r="I5" s="29"/>
       <c r="J5" s="30"/>
-      <c r="K5" s="33" t="s">
+      <c r="K5" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30"/>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="34" t="s">
+      <c r="C6" s="34"/>
+      <c r="D6" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="35"/>
-      <c r="F6" s="34" t="s">
+      <c r="E6" s="34"/>
+      <c r="F6" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="34" t="s">
+      <c r="G6" s="34"/>
+      <c r="H6" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="36"/>
-      <c r="J6" s="37"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="s">
+      <c r="I6" s="35"/>
+      <c r="J6" s="36"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="37"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="36"/>
       <c r="K7" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="L7" s="41" t="s">
+      <c r="L7" s="40" t="s">
         <v>66</v>
       </c>
       <c r="M7" s="17" t="s">
@@ -1934,17 +1943,17 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42"/>
-      <c r="C8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="37"/>
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="41"/>
+      <c r="C8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="36"/>
       <c r="K8" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="43" t="n">
+      <c r="L8" s="42" t="n">
         <v>1</v>
       </c>
       <c r="M8" s="13" t="s">
@@ -1952,58 +1961,58 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42"/>
-      <c r="C9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="44" t="s">
+      <c r="A9" s="41"/>
+      <c r="C9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="L9" s="43" t="n">
+      <c r="L9" s="42" t="n">
         <v>1</v>
       </c>
       <c r="M9" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42"/>
-      <c r="C10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="37"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="45"/>
+      <c r="U9" s="45"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="41"/>
+      <c r="C10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="36"/>
       <c r="K10" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="L10" s="43" t="n">
+      <c r="L10" s="42" t="n">
         <v>4</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="R10" s="45"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="46"/>
-    </row>
-    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42"/>
-      <c r="C11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="37"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="44"/>
+      <c r="T10" s="45"/>
+      <c r="U10" s="45"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="41"/>
+      <c r="C11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="36"/>
       <c r="K11" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="L11" s="47" t="n">
+      <c r="L11" s="46" t="n">
         <v>4</v>
       </c>
       <c r="M11" s="13" t="s">
@@ -2012,22 +2021,22 @@
       <c r="N11" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R11" s="45"/>
-      <c r="S11" s="45"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="46"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="45"/>
+      <c r="U11" s="45"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42"/>
-      <c r="C12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="37"/>
+      <c r="A12" s="41"/>
+      <c r="C12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="36"/>
       <c r="K12" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="L12" s="47" t="n">
+      <c r="L12" s="46" t="n">
         <v>4</v>
       </c>
       <c r="M12" s="13" t="s">
@@ -2036,46 +2045,46 @@
       <c r="N12" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R12" s="45"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="46"/>
-      <c r="U12" s="46"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="45"/>
+      <c r="U12" s="45"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="48"/>
-      <c r="B13" s="49" t="s">
+      <c r="A13" s="47"/>
+      <c r="B13" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="50" t="n">
+      <c r="C13" s="49" t="n">
         <f aca="false">SUM(C7:C12)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="51" t="s">
+      <c r="D13" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="50" t="n">
+      <c r="E13" s="49" t="n">
         <f aca="false">SUM(E7:E12)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="51" t="s">
+      <c r="F13" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="G13" s="50" t="n">
+      <c r="G13" s="49" t="n">
         <f aca="false">SUM(G7:G12)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="51" t="s">
+      <c r="H13" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="50" t="n">
+      <c r="I13" s="49" t="n">
         <f aca="false">SUM(I7:I12)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="37"/>
+      <c r="J13" s="36"/>
       <c r="K13" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="L13" s="47" t="n">
+      <c r="L13" s="46" t="n">
         <v>4</v>
       </c>
       <c r="M13" s="13" t="s">
@@ -2084,32 +2093,32 @@
       <c r="N13" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R13" s="45"/>
-      <c r="S13" s="45"/>
-      <c r="T13" s="46"/>
-      <c r="U13" s="46"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="45"/>
+      <c r="U13" s="45"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="53"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="55" t="s">
+      <c r="B14" s="52"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="E14" s="56"/>
-      <c r="F14" s="55" t="s">
+      <c r="E14" s="55"/>
+      <c r="F14" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="G14" s="54"/>
-      <c r="H14" s="53" t="s">
+      <c r="G14" s="53"/>
+      <c r="H14" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="I14" s="54" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="37"/>
+      <c r="I14" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" s="36"/>
       <c r="K14" s="13" t="s">
         <v>86</v>
       </c>
@@ -2119,44 +2128,44 @@
       <c r="M14" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="46"/>
-      <c r="U14" s="46"/>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="45"/>
+      <c r="U14" s="45"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="57"/>
-      <c r="C15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="G15" s="40"/>
+      <c r="A15" s="56"/>
+      <c r="C15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="G15" s="39"/>
       <c r="H15" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="I15" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="37"/>
+      <c r="I15" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="36"/>
       <c r="K15" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="L15" s="47" t="n">
+      <c r="L15" s="46" t="n">
         <v>4</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="57"/>
-      <c r="C16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="37"/>
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="56"/>
+      <c r="C16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="36"/>
       <c r="K16" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="L16" s="47" t="n">
+      <c r="L16" s="46" t="n">
         <v>4</v>
       </c>
       <c r="M16" s="13" t="s">
@@ -2165,15 +2174,15 @@
       <c r="N16" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Q16" s="46"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="57"/>
-      <c r="C17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="37"/>
+      <c r="Q16" s="45"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="56"/>
+      <c r="C17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="36"/>
       <c r="K17" s="13" t="s">
         <v>94</v>
       </c>
@@ -2186,15 +2195,15 @@
       <c r="N17" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="Q17" s="46"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="57"/>
-      <c r="C18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="37"/>
+      <c r="Q17" s="45"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="56"/>
+      <c r="C18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="36"/>
       <c r="K18" s="13" t="s">
         <v>97</v>
       </c>
@@ -2204,18 +2213,18 @@
       <c r="M18" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="Q18" s="46"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="57"/>
-      <c r="C19" s="40" t="n">
+      <c r="Q18" s="45"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="56"/>
+      <c r="C19" s="39" t="n">
         <v>84</v>
       </c>
-      <c r="E19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="44" t="s">
+      <c r="E19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="43" t="s">
         <v>15</v>
       </c>
       <c r="L19" s="14" t="n">
@@ -2224,40 +2233,40 @@
       <c r="M19" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="Q19" s="46"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="58"/>
-      <c r="B20" s="49" t="s">
+      <c r="Q19" s="45"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="57"/>
+      <c r="B20" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="50" t="n">
+      <c r="C20" s="49" t="n">
         <f aca="false">SUM(C14:C19)</f>
         <v>84</v>
       </c>
-      <c r="D20" s="51" t="s">
+      <c r="D20" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="50" t="n">
+      <c r="E20" s="49" t="n">
         <f aca="false">SUM(E14:E19)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="51" t="s">
+      <c r="F20" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="59" t="n">
+      <c r="G20" s="58" t="n">
         <f aca="false">SUM(G14:G19)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="49" t="s">
+      <c r="H20" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="I20" s="50" t="n">
+      <c r="I20" s="49" t="n">
         <f aca="false">SUM(I14:I19)</f>
         <v>8</v>
       </c>
-      <c r="J20" s="37"/>
-      <c r="K20" s="60" t="s">
+      <c r="J20" s="36"/>
+      <c r="K20" s="59" t="s">
         <v>100</v>
       </c>
       <c r="L20" s="14" t="n">
@@ -2266,37 +2275,37 @@
       <c r="M20" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="O20" s="46"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="46"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="45"/>
     </row>
     <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="61" t="s">
+      <c r="A21" s="60" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="C21" s="54" t="n">
+      <c r="C21" s="53" t="n">
         <v>5</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="E21" s="54" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="62" t="s">
+      <c r="E21" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="54" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="55" t="s">
+      <c r="G21" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="54" t="s">
         <v>84</v>
       </c>
       <c r="I21" s="1"/>
-      <c r="J21" s="37"/>
+      <c r="J21" s="36"/>
       <c r="K21" s="13" t="s">
         <v>100</v>
       </c>
@@ -2306,32 +2315,33 @@
       <c r="M21" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="O21" s="46"/>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="46"/>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="63"/>
-      <c r="B22" s="39" t="s">
+      <c r="O21" s="45"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="45"/>
+    </row>
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="62"/>
+      <c r="B22" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" s="39" t="s">
+      <c r="C22" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" s="39" t="s">
+      <c r="E22" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="38"/>
+      <c r="G22" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="G22" s="40" t="n">
-        <v>4</v>
-      </c>
       <c r="I22" s="1"/>
-      <c r="J22" s="37"/>
+      <c r="J22" s="36"/>
       <c r="K22" s="13" t="s">
         <v>100</v>
       </c>
@@ -2341,83 +2351,83 @@
       <c r="M22" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="N22" s="46"/>
-      <c r="O22" s="46"/>
-      <c r="P22" s="46"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="63"/>
-      <c r="B23" s="39" t="s">
+      <c r="N22" s="45"/>
+      <c r="O22" s="45"/>
+      <c r="P22" s="45"/>
+    </row>
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="62"/>
+      <c r="B23" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" s="39" t="s">
+      <c r="C23" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="40" t="n">
+      <c r="E23" s="39" t="n">
         <v>4</v>
       </c>
       <c r="F23" s="1"/>
-      <c r="G23" s="64"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="37"/>
+      <c r="G23" s="63"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="36"/>
       <c r="K23" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="L23" s="43" t="n">
+      <c r="L23" s="42" t="n">
         <v>4</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="N23" s="46"/>
+      <c r="N23" s="45"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="63"/>
-      <c r="B24" s="39" t="s">
+      <c r="A24" s="62"/>
+      <c r="B24" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C24" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" s="39" t="s">
+      <c r="C24" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="64"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="60" t="s">
+      <c r="E24" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="38"/>
+      <c r="G24" s="63"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="L24" s="47" t="n">
+      <c r="L24" s="46" t="n">
         <v>5</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="N24" s="46" t="s">
+      <c r="N24" s="45" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="63"/>
+    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="62"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="37"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="36"/>
       <c r="K25" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="L25" s="43" t="n">
+      <c r="L25" s="42" t="n">
         <v>5</v>
       </c>
       <c r="M25" s="13" t="s">
@@ -2427,19 +2437,19 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="63"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="44" t="s">
+    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="62"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="L26" s="43" t="n">
+      <c r="L26" s="42" t="n">
         <v>4</v>
       </c>
       <c r="M26" s="13" t="s">
@@ -2449,70 +2459,70 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="58"/>
-      <c r="B27" s="49" t="s">
+    <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="57"/>
+      <c r="B27" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="C27" s="50" t="n">
+      <c r="C27" s="49" t="n">
         <f aca="false">SUM(C21:C26)</f>
         <v>17</v>
       </c>
-      <c r="D27" s="51" t="s">
+      <c r="D27" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="E27" s="50" t="n">
+      <c r="E27" s="49" t="n">
         <f aca="false">SUM(E21:E26)</f>
         <v>16</v>
       </c>
-      <c r="F27" s="51" t="s">
+      <c r="F27" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="G27" s="50" t="n">
+      <c r="G27" s="49" t="n">
         <f aca="false">SUM(G21:G26)</f>
         <v>8</v>
       </c>
-      <c r="H27" s="51" t="s">
+      <c r="H27" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="I27" s="50" t="n">
+      <c r="I27" s="49" t="n">
         <f aca="false">SUM(I21:I26)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="37"/>
-      <c r="L27" s="43"/>
+      <c r="J27" s="36"/>
+      <c r="L27" s="42"/>
     </row>
     <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="57" t="s">
+      <c r="A28" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="B28" s="55" t="s">
+      <c r="B28" s="54" t="s">
         <v>84</v>
       </c>
       <c r="C28" s="1"/>
-      <c r="D28" s="53" t="s">
+      <c r="D28" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="E28" s="65" t="n">
+      <c r="E28" s="64" t="n">
         <v>4</v>
       </c>
       <c r="F28" s="1"/>
-      <c r="G28" s="54"/>
+      <c r="G28" s="53"/>
       <c r="H28" s="1"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="44" t="s">
+      <c r="I28" s="53"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="L28" s="43" t="n">
+      <c r="L28" s="42" t="n">
         <v>4</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="57"/>
+    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="56"/>
       <c r="B29" s="14" t="s">
         <v>124</v>
       </c>
@@ -2524,38 +2534,38 @@
         <v>4</v>
       </c>
       <c r="F29" s="1"/>
-      <c r="G29" s="40"/>
+      <c r="G29" s="39"/>
       <c r="H29" s="1"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="37"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="36"/>
       <c r="K29" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="L29" s="47" t="n">
+      <c r="L29" s="46" t="n">
         <v>4</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="57"/>
+    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="56"/>
       <c r="C30" s="1"/>
-      <c r="D30" s="39" t="s">
+      <c r="D30" s="1" t="s">
         <v>126</v>
       </c>
       <c r="E30" s="15" t="n">
         <v>4</v>
       </c>
       <c r="F30" s="1"/>
-      <c r="G30" s="40"/>
+      <c r="G30" s="39"/>
       <c r="H30" s="1"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="37"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="36"/>
       <c r="K30" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="L30" s="47" t="n">
+      <c r="L30" s="46" t="n">
         <v>4</v>
       </c>
       <c r="M30" s="13" t="s">
@@ -2563,7 +2573,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="57"/>
+      <c r="A31" s="56"/>
       <c r="C31" s="1"/>
       <c r="D31" s="14" t="s">
         <v>127</v>
@@ -2572,13 +2582,13 @@
         <v>4</v>
       </c>
       <c r="F31" s="1"/>
-      <c r="G31" s="40"/>
+      <c r="G31" s="39"/>
       <c r="H31" s="1"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="37"/>
-    </row>
-    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="57"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="56"/>
       <c r="C32" s="1"/>
       <c r="D32" s="14" t="s">
         <v>128</v>
@@ -2587,25 +2597,25 @@
         <v>1</v>
       </c>
       <c r="F32" s="1"/>
-      <c r="G32" s="40"/>
+      <c r="G32" s="39"/>
       <c r="H32" s="1"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="66" t="s">
+      <c r="I32" s="39"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="65" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="57"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="67" t="s">
+    <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="56"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="F33" s="39"/>
-      <c r="G33" s="40"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="37"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="36"/>
       <c r="K33" s="13" t="s">
         <v>131</v>
       </c>
@@ -2616,37 +2626,37 @@
         <v>133</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="68"/>
-      <c r="B34" s="49" t="s">
+    <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="67"/>
+      <c r="B34" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="C34" s="50" t="n">
+      <c r="C34" s="49" t="n">
         <f aca="false">SUM(C28:C33)</f>
         <v>0</v>
       </c>
-      <c r="D34" s="51" t="s">
+      <c r="D34" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="50" t="n">
+      <c r="E34" s="49" t="n">
         <f aca="false">SUM(E28:E33)</f>
         <v>17</v>
       </c>
-      <c r="F34" s="51" t="s">
+      <c r="F34" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="G34" s="59" t="n">
+      <c r="G34" s="58" t="n">
         <f aca="false">SUM(G28:G33)</f>
         <v>0</v>
       </c>
-      <c r="H34" s="49" t="s">
+      <c r="H34" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="I34" s="50" t="n">
+      <c r="I34" s="49" t="n">
         <f aca="false">SUM(I28:I33)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="37"/>
+      <c r="J34" s="36"/>
       <c r="K34" s="13" t="s">
         <v>134</v>
       </c>
@@ -2661,15 +2671,15 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="69" t="s">
+      <c r="A35" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="B35" s="39"/>
-      <c r="C35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="G35" s="40"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="37"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="36"/>
       <c r="K35" s="13" t="s">
         <v>137</v>
       </c>
@@ -2683,14 +2693,14 @@
         <v>138</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="63"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="37"/>
+    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="62"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="36"/>
       <c r="K36" s="13" t="s">
         <v>139</v>
       </c>
@@ -2704,14 +2714,14 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="63"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="40"/>
-      <c r="E37" s="40"/>
-      <c r="G37" s="70"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="37"/>
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="62"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="G37" s="69"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="36"/>
       <c r="K37" s="13" t="s">
         <v>141</v>
       </c>
@@ -2725,14 +2735,14 @@
         <v>142</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="63"/>
-      <c r="B38" s="39"/>
-      <c r="C38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="G38" s="70"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="37"/>
+    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="62"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="G38" s="69"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="36"/>
       <c r="K38" s="13" t="s">
         <v>143</v>
       </c>
@@ -2746,15 +2756,15 @@
         <v>145</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="63"/>
-      <c r="B39" s="39"/>
-      <c r="C39" s="40"/>
-      <c r="E39" s="40"/>
-      <c r="G39" s="70"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="37"/>
-      <c r="K39" s="44" t="s">
+    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="62"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="G39" s="69"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="36"/>
+      <c r="K39" s="43" t="s">
         <v>27</v>
       </c>
       <c r="L39" s="14" t="n">
@@ -2767,15 +2777,15 @@
         <v>147</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="63"/>
-      <c r="B40" s="39"/>
-      <c r="C40" s="40"/>
-      <c r="E40" s="40"/>
-      <c r="G40" s="70"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="37"/>
-      <c r="K40" s="44" t="s">
+    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="62"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="G40" s="69"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="43" t="s">
         <v>148</v>
       </c>
       <c r="M40" s="13" t="s">
@@ -2785,253 +2795,253 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="58"/>
-      <c r="B41" s="49" t="s">
+    <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="57"/>
+      <c r="B41" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="50" t="n">
+      <c r="C41" s="49" t="n">
         <f aca="false">SUM(C35:C40)</f>
         <v>0</v>
       </c>
-      <c r="D41" s="51" t="s">
+      <c r="D41" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="E41" s="50" t="n">
+      <c r="E41" s="49" t="n">
         <f aca="false">SUM(E35:E40)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="51" t="s">
+      <c r="F41" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="G41" s="50" t="n">
+      <c r="G41" s="49" t="n">
         <f aca="false">SUM(G35:G40)</f>
         <v>0</v>
       </c>
-      <c r="H41" s="51" t="s">
+      <c r="H41" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="I41" s="50" t="n">
+      <c r="I41" s="49" t="n">
         <f aca="false">SUM(I35:I40)</f>
         <v>0</v>
       </c>
-      <c r="J41" s="37"/>
+      <c r="J41" s="36"/>
       <c r="K41" s="17"/>
     </row>
-    <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="71" t="s">
+    <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="70" t="s">
         <v>151</v>
       </c>
-      <c r="B42" s="72"/>
-      <c r="C42" s="64"/>
-      <c r="D42" s="72"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="64"/>
-      <c r="H42" s="72"/>
-      <c r="I42" s="64"/>
-      <c r="J42" s="73"/>
-      <c r="K42" s="66" t="s">
+      <c r="B42" s="71"/>
+      <c r="C42" s="63"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="65" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J43" s="73"/>
+    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J43" s="72"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="74" t="s">
+      <c r="A44" s="73" t="s">
         <v>153</v>
       </c>
-      <c r="B44" s="74"/>
-      <c r="C44" s="74"/>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="74"/>
-      <c r="H44" s="74"/>
-      <c r="I44" s="74"/>
-      <c r="J44" s="74"/>
+      <c r="B44" s="73"/>
+      <c r="C44" s="73"/>
+      <c r="D44" s="73"/>
+      <c r="E44" s="73"/>
+      <c r="F44" s="73"/>
+      <c r="G44" s="73"/>
+      <c r="H44" s="73"/>
+      <c r="I44" s="73"/>
+      <c r="J44" s="73"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="74"/>
-      <c r="B45" s="74"/>
-      <c r="C45" s="74"/>
-      <c r="D45" s="74"/>
-      <c r="E45" s="74"/>
-      <c r="F45" s="74"/>
-      <c r="G45" s="74"/>
-      <c r="H45" s="74"/>
-      <c r="I45" s="74"/>
-      <c r="J45" s="74"/>
+      <c r="A45" s="73"/>
+      <c r="B45" s="73"/>
+      <c r="C45" s="73"/>
+      <c r="D45" s="73"/>
+      <c r="E45" s="73"/>
+      <c r="F45" s="73"/>
+      <c r="G45" s="73"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="73"/>
+      <c r="J45" s="73"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="74"/>
-      <c r="B46" s="74"/>
-      <c r="C46" s="74"/>
-      <c r="D46" s="74"/>
-      <c r="E46" s="74"/>
-      <c r="F46" s="74"/>
-      <c r="G46" s="74"/>
-      <c r="H46" s="74"/>
-      <c r="I46" s="74"/>
-      <c r="J46" s="74"/>
+      <c r="A46" s="73"/>
+      <c r="B46" s="73"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="73"/>
+      <c r="F46" s="73"/>
+      <c r="G46" s="73"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="73"/>
+      <c r="J46" s="73"/>
       <c r="M46" s="17"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="74"/>
-      <c r="B47" s="74"/>
-      <c r="C47" s="74"/>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="74"/>
-      <c r="H47" s="74"/>
-      <c r="I47" s="74"/>
-      <c r="J47" s="74"/>
+      <c r="A47" s="73"/>
+      <c r="B47" s="73"/>
+      <c r="C47" s="73"/>
+      <c r="D47" s="73"/>
+      <c r="E47" s="73"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="73"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73"/>
+      <c r="J47" s="73"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="74"/>
-      <c r="B48" s="74"/>
-      <c r="C48" s="74"/>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="74"/>
-      <c r="H48" s="74"/>
-      <c r="I48" s="74"/>
-      <c r="J48" s="74"/>
+      <c r="A48" s="73"/>
+      <c r="B48" s="73"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="73"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="73"/>
+      <c r="I48" s="73"/>
+      <c r="J48" s="73"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="74"/>
-      <c r="B49" s="74"/>
-      <c r="C49" s="74"/>
-      <c r="D49" s="74"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="74"/>
-      <c r="H49" s="74"/>
-      <c r="I49" s="74"/>
-      <c r="J49" s="74"/>
+      <c r="A49" s="73"/>
+      <c r="B49" s="73"/>
+      <c r="C49" s="73"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="73"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73"/>
+      <c r="J49" s="73"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="74"/>
-      <c r="B50" s="74"/>
-      <c r="C50" s="74"/>
-      <c r="D50" s="74"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="74"/>
-      <c r="H50" s="74"/>
-      <c r="I50" s="74"/>
-      <c r="J50" s="74"/>
+      <c r="A50" s="73"/>
+      <c r="B50" s="73"/>
+      <c r="C50" s="73"/>
+      <c r="D50" s="73"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="73"/>
+      <c r="G50" s="73"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73"/>
+      <c r="J50" s="73"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="74"/>
-      <c r="B51" s="74"/>
-      <c r="C51" s="74"/>
-      <c r="D51" s="74"/>
-      <c r="E51" s="74"/>
-      <c r="F51" s="74"/>
-      <c r="G51" s="74"/>
-      <c r="H51" s="74"/>
-      <c r="I51" s="74"/>
-      <c r="J51" s="74"/>
+      <c r="A51" s="73"/>
+      <c r="B51" s="73"/>
+      <c r="C51" s="73"/>
+      <c r="D51" s="73"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="73"/>
+      <c r="G51" s="73"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73"/>
+      <c r="J51" s="73"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="74"/>
-      <c r="B52" s="74"/>
-      <c r="C52" s="74"/>
-      <c r="D52" s="74"/>
-      <c r="E52" s="74"/>
-      <c r="F52" s="74"/>
-      <c r="G52" s="74"/>
-      <c r="H52" s="74"/>
-      <c r="I52" s="74"/>
-      <c r="J52" s="74"/>
+      <c r="A52" s="73"/>
+      <c r="B52" s="73"/>
+      <c r="C52" s="73"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="73"/>
+      <c r="G52" s="73"/>
+      <c r="H52" s="73"/>
+      <c r="I52" s="73"/>
+      <c r="J52" s="73"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="74"/>
-      <c r="B53" s="74"/>
-      <c r="C53" s="74"/>
-      <c r="D53" s="74"/>
-      <c r="E53" s="74"/>
-      <c r="F53" s="74"/>
-      <c r="G53" s="74"/>
-      <c r="H53" s="74"/>
-      <c r="I53" s="74"/>
-      <c r="J53" s="74"/>
+      <c r="A53" s="73"/>
+      <c r="B53" s="73"/>
+      <c r="C53" s="73"/>
+      <c r="D53" s="73"/>
+      <c r="E53" s="73"/>
+      <c r="F53" s="73"/>
+      <c r="G53" s="73"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73"/>
+      <c r="J53" s="73"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="74"/>
-      <c r="B54" s="74"/>
-      <c r="C54" s="74"/>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="74"/>
-      <c r="H54" s="74"/>
-      <c r="I54" s="74"/>
-      <c r="J54" s="74"/>
+      <c r="A54" s="73"/>
+      <c r="B54" s="73"/>
+      <c r="C54" s="73"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="73"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73"/>
+      <c r="J54" s="73"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="74"/>
-      <c r="B55" s="74"/>
-      <c r="C55" s="74"/>
-      <c r="D55" s="74"/>
-      <c r="E55" s="74"/>
-      <c r="F55" s="74"/>
-      <c r="G55" s="74"/>
-      <c r="H55" s="74"/>
-      <c r="I55" s="74"/>
-      <c r="J55" s="74"/>
+      <c r="A55" s="73"/>
+      <c r="B55" s="73"/>
+      <c r="C55" s="73"/>
+      <c r="D55" s="73"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="73"/>
+      <c r="G55" s="73"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73"/>
+      <c r="J55" s="73"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="74"/>
-      <c r="B56" s="74"/>
-      <c r="C56" s="74"/>
-      <c r="D56" s="74"/>
-      <c r="E56" s="74"/>
-      <c r="F56" s="74"/>
-      <c r="G56" s="74"/>
-      <c r="H56" s="74"/>
-      <c r="I56" s="74"/>
-      <c r="J56" s="74"/>
+      <c r="A56" s="73"/>
+      <c r="B56" s="73"/>
+      <c r="C56" s="73"/>
+      <c r="D56" s="73"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="73"/>
+      <c r="G56" s="73"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73"/>
+      <c r="J56" s="73"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="74"/>
-      <c r="B57" s="74"/>
-      <c r="C57" s="74"/>
-      <c r="D57" s="74"/>
-      <c r="E57" s="74"/>
-      <c r="F57" s="74"/>
-      <c r="G57" s="74"/>
-      <c r="H57" s="74"/>
-      <c r="I57" s="74"/>
-      <c r="J57" s="74"/>
+      <c r="A57" s="73"/>
+      <c r="B57" s="73"/>
+      <c r="C57" s="73"/>
+      <c r="D57" s="73"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="73"/>
+      <c r="G57" s="73"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73"/>
+      <c r="J57" s="73"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="74"/>
-      <c r="B58" s="74"/>
-      <c r="C58" s="74"/>
-      <c r="D58" s="74"/>
-      <c r="E58" s="74"/>
-      <c r="F58" s="74"/>
-      <c r="G58" s="74"/>
-      <c r="H58" s="74"/>
-      <c r="I58" s="74"/>
-      <c r="J58" s="74"/>
+      <c r="A58" s="73"/>
+      <c r="B58" s="73"/>
+      <c r="C58" s="73"/>
+      <c r="D58" s="73"/>
+      <c r="E58" s="73"/>
+      <c r="F58" s="73"/>
+      <c r="G58" s="73"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73"/>
+      <c r="J58" s="73"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="74"/>
-      <c r="B59" s="74"/>
-      <c r="C59" s="74"/>
-      <c r="D59" s="74"/>
-      <c r="E59" s="74"/>
-      <c r="F59" s="74"/>
-      <c r="G59" s="74"/>
-      <c r="H59" s="74"/>
-      <c r="I59" s="74"/>
-      <c r="J59" s="74"/>
+      <c r="A59" s="73"/>
+      <c r="B59" s="73"/>
+      <c r="C59" s="73"/>
+      <c r="D59" s="73"/>
+      <c r="E59" s="73"/>
+      <c r="F59" s="73"/>
+      <c r="G59" s="73"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73"/>
+      <c r="J59" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3086,7 +3096,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="21" min="15" style="13" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
         <v>49</v>
       </c>
@@ -3174,44 +3184,44 @@
       <c r="H5" s="28"/>
       <c r="I5" s="29"/>
       <c r="J5" s="30"/>
-      <c r="K5" s="33" t="s">
+      <c r="K5" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="30"/>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="34" t="s">
+      <c r="C6" s="34"/>
+      <c r="D6" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="35"/>
-      <c r="F6" s="34" t="s">
+      <c r="E6" s="34"/>
+      <c r="F6" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="34" t="s">
+      <c r="G6" s="34"/>
+      <c r="H6" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="36"/>
-      <c r="J6" s="37"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="s">
+      <c r="I6" s="35"/>
+      <c r="J6" s="36"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="37"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="36"/>
       <c r="K7" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="L7" s="41" t="s">
+      <c r="L7" s="40" t="s">
         <v>66</v>
       </c>
       <c r="M7" s="17" t="s">
@@ -3221,17 +3231,17 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42"/>
-      <c r="C8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="37"/>
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="41"/>
+      <c r="C8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="36"/>
       <c r="K8" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="43" t="n">
+      <c r="L8" s="42" t="n">
         <v>1</v>
       </c>
       <c r="M8" s="13" t="s">
@@ -3239,58 +3249,58 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42"/>
-      <c r="C9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="44" t="s">
+      <c r="A9" s="41"/>
+      <c r="C9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="L9" s="43" t="n">
+      <c r="L9" s="42" t="n">
         <v>1</v>
       </c>
       <c r="M9" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42"/>
-      <c r="C10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="37"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="45"/>
+      <c r="U9" s="45"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="41"/>
+      <c r="C10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="36"/>
       <c r="K10" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="L10" s="43" t="n">
+      <c r="L10" s="42" t="n">
         <v>4</v>
       </c>
       <c r="M10" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="R10" s="45"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="46"/>
-    </row>
-    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42"/>
-      <c r="C11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="37"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="44"/>
+      <c r="T10" s="45"/>
+      <c r="U10" s="45"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="41"/>
+      <c r="C11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="36"/>
       <c r="K11" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="L11" s="47" t="n">
+      <c r="L11" s="46" t="n">
         <v>4</v>
       </c>
       <c r="M11" s="13" t="s">
@@ -3299,22 +3309,22 @@
       <c r="N11" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R11" s="45"/>
-      <c r="S11" s="45"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="46"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="45"/>
+      <c r="U11" s="45"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42"/>
-      <c r="C12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="37"/>
+      <c r="A12" s="41"/>
+      <c r="C12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="36"/>
       <c r="K12" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="L12" s="47" t="n">
+      <c r="L12" s="46" t="n">
         <v>4</v>
       </c>
       <c r="M12" s="13" t="s">
@@ -3323,46 +3333,46 @@
       <c r="N12" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R12" s="45"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="46"/>
-      <c r="U12" s="46"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="45"/>
+      <c r="U12" s="45"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="48"/>
-      <c r="B13" s="49" t="s">
+      <c r="A13" s="47"/>
+      <c r="B13" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="50" t="n">
+      <c r="C13" s="49" t="n">
         <f aca="false">SUM(C7:C12)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="51" t="s">
+      <c r="D13" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="50" t="n">
+      <c r="E13" s="49" t="n">
         <f aca="false">SUM(E7:E12)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="51" t="s">
+      <c r="F13" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="G13" s="50" t="n">
+      <c r="G13" s="49" t="n">
         <f aca="false">SUM(G7:G12)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="51" t="s">
+      <c r="H13" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="50" t="n">
+      <c r="I13" s="49" t="n">
         <f aca="false">SUM(I7:I12)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="37"/>
+      <c r="J13" s="36"/>
       <c r="K13" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="L13" s="47" t="n">
+      <c r="L13" s="46" t="n">
         <v>4</v>
       </c>
       <c r="M13" s="13" t="s">
@@ -3371,32 +3381,32 @@
       <c r="N13" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="R13" s="45"/>
-      <c r="S13" s="45"/>
-      <c r="T13" s="46"/>
-      <c r="U13" s="46"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="45"/>
+      <c r="U13" s="45"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="53"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="55" t="s">
+      <c r="B14" s="52"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="E14" s="56"/>
-      <c r="F14" s="55" t="s">
+      <c r="E14" s="55"/>
+      <c r="F14" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="G14" s="54"/>
-      <c r="H14" s="53" t="s">
+      <c r="G14" s="53"/>
+      <c r="H14" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="I14" s="54" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="37"/>
+      <c r="I14" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" s="36"/>
       <c r="K14" s="13" t="s">
         <v>86</v>
       </c>
@@ -3406,44 +3416,44 @@
       <c r="M14" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="46"/>
-      <c r="U14" s="46"/>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="45"/>
+      <c r="U14" s="45"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="57"/>
-      <c r="C15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="G15" s="40"/>
+      <c r="A15" s="56"/>
+      <c r="C15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="G15" s="39"/>
       <c r="H15" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="I15" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="37"/>
+      <c r="I15" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="36"/>
       <c r="K15" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="L15" s="47" t="n">
+      <c r="L15" s="46" t="n">
         <v>4</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="57"/>
-      <c r="C16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="37"/>
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="56"/>
+      <c r="C16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="36"/>
       <c r="K16" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="L16" s="47" t="n">
+      <c r="L16" s="46" t="n">
         <v>4</v>
       </c>
       <c r="M16" s="13" t="s">
@@ -3452,15 +3462,15 @@
       <c r="N16" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Q16" s="46"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="57"/>
-      <c r="C17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="37"/>
+      <c r="Q16" s="45"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="56"/>
+      <c r="C17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="36"/>
       <c r="K17" s="13" t="s">
         <v>94</v>
       </c>
@@ -3473,15 +3483,15 @@
       <c r="N17" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="Q17" s="46"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="57"/>
-      <c r="C18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="37"/>
+      <c r="Q17" s="45"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="56"/>
+      <c r="C18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="36"/>
       <c r="K18" s="13" t="s">
         <v>97</v>
       </c>
@@ -3491,18 +3501,18 @@
       <c r="M18" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="Q18" s="46"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="57"/>
-      <c r="C19" s="40" t="n">
+      <c r="Q18" s="45"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="56"/>
+      <c r="C19" s="39" t="n">
         <v>84</v>
       </c>
-      <c r="E19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="44" t="s">
+      <c r="E19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="43" t="s">
         <v>15</v>
       </c>
       <c r="L19" s="14" t="n">
@@ -3511,40 +3521,40 @@
       <c r="M19" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="Q19" s="46"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="58"/>
-      <c r="B20" s="49" t="s">
+      <c r="Q19" s="45"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="57"/>
+      <c r="B20" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="50" t="n">
+      <c r="C20" s="49" t="n">
         <f aca="false">SUM(C14:C19)</f>
         <v>84</v>
       </c>
-      <c r="D20" s="51" t="s">
+      <c r="D20" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="50" t="n">
+      <c r="E20" s="49" t="n">
         <f aca="false">SUM(E14:E19)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="51" t="s">
+      <c r="F20" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="59" t="n">
+      <c r="G20" s="58" t="n">
         <f aca="false">SUM(G14:G19)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="49" t="s">
+      <c r="H20" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="I20" s="50" t="n">
+      <c r="I20" s="49" t="n">
         <f aca="false">SUM(I14:I19)</f>
         <v>8</v>
       </c>
-      <c r="J20" s="37"/>
-      <c r="K20" s="60" t="s">
+      <c r="J20" s="36"/>
+      <c r="K20" s="59" t="s">
         <v>100</v>
       </c>
       <c r="L20" s="14" t="n">
@@ -3553,35 +3563,35 @@
       <c r="M20" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="O20" s="46"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="46"/>
-    </row>
-    <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="61" t="s">
+      <c r="O20" s="45"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="45"/>
+    </row>
+    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="60" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="C21" s="54" t="n">
+      <c r="C21" s="53" t="n">
         <v>5</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="E21" s="54" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="0"/>
-      <c r="G21" s="54" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="55" t="s">
+      <c r="E21" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="54" t="s">
         <v>84</v>
       </c>
       <c r="I21" s="1"/>
-      <c r="J21" s="37"/>
+      <c r="J21" s="36"/>
       <c r="K21" s="13" t="s">
         <v>100</v>
       </c>
@@ -3591,32 +3601,32 @@
       <c r="M21" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="O21" s="46"/>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="46"/>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="63"/>
-      <c r="B22" s="39" t="s">
+      <c r="O21" s="45"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="45"/>
+    </row>
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="62"/>
+      <c r="B22" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" s="39" t="s">
+      <c r="C22" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" s="39" t="s">
+      <c r="E22" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="G22" s="40" t="n">
+      <c r="G22" s="39" t="n">
         <v>4</v>
       </c>
       <c r="I22" s="1"/>
-      <c r="J22" s="37"/>
+      <c r="J22" s="36"/>
       <c r="K22" s="13" t="s">
         <v>100</v>
       </c>
@@ -3626,83 +3636,83 @@
       <c r="M22" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="N22" s="46"/>
-      <c r="O22" s="46"/>
-      <c r="P22" s="46"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="63"/>
-      <c r="B23" s="39" t="s">
+      <c r="N22" s="45"/>
+      <c r="O22" s="45"/>
+      <c r="P22" s="45"/>
+    </row>
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="62"/>
+      <c r="B23" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" s="39" t="s">
+      <c r="C23" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="40" t="n">
+      <c r="E23" s="39" t="n">
         <v>4</v>
       </c>
       <c r="F23" s="1"/>
-      <c r="G23" s="64"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="37"/>
+      <c r="G23" s="63"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="36"/>
       <c r="K23" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="L23" s="43" t="n">
+      <c r="L23" s="42" t="n">
         <v>4</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="N23" s="46"/>
+      <c r="N23" s="45"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="63"/>
-      <c r="B24" s="39" t="s">
+      <c r="A24" s="62"/>
+      <c r="B24" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C24" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" s="62" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="64"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="60" t="s">
+      <c r="C24" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="61" t="s">
+        <v>154</v>
+      </c>
+      <c r="E24" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="38"/>
+      <c r="G24" s="63"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="L24" s="47" t="n">
+      <c r="L24" s="46" t="n">
         <v>5</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="N24" s="46" t="s">
+      <c r="N24" s="45" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="63"/>
+    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="62"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="37"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="36"/>
       <c r="K25" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="L25" s="43" t="n">
+      <c r="L25" s="42" t="n">
         <v>5</v>
       </c>
       <c r="M25" s="13" t="s">
@@ -3712,19 +3722,19 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="63"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="44" t="s">
+    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="62"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="L26" s="43" t="n">
+      <c r="L26" s="42" t="n">
         <v>4</v>
       </c>
       <c r="M26" s="13" t="s">
@@ -3734,113 +3744,113 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="58"/>
-      <c r="B27" s="49" t="s">
+    <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="57"/>
+      <c r="B27" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="C27" s="50" t="n">
+      <c r="C27" s="49" t="n">
         <f aca="false">SUM(C21:C26)</f>
         <v>17</v>
       </c>
-      <c r="D27" s="51" t="s">
+      <c r="D27" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="E27" s="50" t="n">
+      <c r="E27" s="49" t="n">
         <f aca="false">SUM(E21:E26)</f>
         <v>16</v>
       </c>
-      <c r="F27" s="51" t="s">
+      <c r="F27" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="G27" s="50" t="n">
+      <c r="G27" s="49" t="n">
         <f aca="false">SUM(G21:G26)</f>
         <v>8</v>
       </c>
-      <c r="H27" s="51" t="s">
+      <c r="H27" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="I27" s="50" t="n">
+      <c r="I27" s="49" t="n">
         <f aca="false">SUM(I21:I26)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="37"/>
-      <c r="L27" s="43"/>
+      <c r="J27" s="36"/>
+      <c r="L27" s="42"/>
     </row>
     <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="57" t="s">
+      <c r="A28" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="B28" s="55" t="s">
+      <c r="B28" s="54" t="s">
         <v>84</v>
       </c>
       <c r="C28" s="1"/>
-      <c r="D28" s="53" t="s">
+      <c r="D28" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="E28" s="65" t="n">
+      <c r="E28" s="64" t="n">
         <v>4</v>
       </c>
       <c r="F28" s="1"/>
-      <c r="G28" s="54"/>
+      <c r="G28" s="53"/>
       <c r="H28" s="1"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="44" t="s">
+      <c r="I28" s="53"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="L28" s="43" t="n">
+      <c r="L28" s="42" t="n">
         <v>4</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="57"/>
+    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="56"/>
       <c r="B29" s="14" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="E29" s="15" t="n">
         <v>4</v>
       </c>
       <c r="F29" s="1"/>
-      <c r="G29" s="40"/>
+      <c r="G29" s="39"/>
       <c r="H29" s="1"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="37"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="36"/>
       <c r="K29" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="L29" s="47" t="n">
+      <c r="L29" s="46" t="n">
         <v>4</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="57"/>
+    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="56"/>
       <c r="C30" s="1"/>
-      <c r="D30" s="39" t="s">
-        <v>126</v>
+      <c r="D30" s="38" t="s">
+        <v>157</v>
       </c>
       <c r="E30" s="15" t="n">
         <v>4</v>
       </c>
       <c r="F30" s="1"/>
-      <c r="G30" s="40"/>
+      <c r="G30" s="39"/>
       <c r="H30" s="1"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="37"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="36"/>
       <c r="K30" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="L30" s="47" t="n">
+      <c r="L30" s="46" t="n">
         <v>4</v>
       </c>
       <c r="M30" s="13" t="s">
@@ -3848,22 +3858,22 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="57"/>
+      <c r="A31" s="56"/>
       <c r="C31" s="1"/>
       <c r="D31" s="14" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="E31" s="15" t="n">
         <v>4</v>
       </c>
       <c r="F31" s="1"/>
-      <c r="G31" s="40"/>
+      <c r="G31" s="39"/>
       <c r="H31" s="1"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="37"/>
-    </row>
-    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="57"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="36"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="56"/>
       <c r="C32" s="1"/>
       <c r="D32" s="14" t="s">
         <v>128</v>
@@ -3872,25 +3882,25 @@
         <v>1</v>
       </c>
       <c r="F32" s="1"/>
-      <c r="G32" s="40"/>
+      <c r="G32" s="39"/>
       <c r="H32" s="1"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="66" t="s">
+      <c r="I32" s="39"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="65" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="57"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="67" t="s">
+    <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="56"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="F33" s="39"/>
-      <c r="G33" s="40"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="37"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="36"/>
       <c r="K33" s="13" t="s">
         <v>131</v>
       </c>
@@ -3901,37 +3911,37 @@
         <v>133</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="68"/>
-      <c r="B34" s="49" t="s">
+    <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="67"/>
+      <c r="B34" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="C34" s="50" t="n">
+      <c r="C34" s="49" t="n">
         <f aca="false">SUM(C28:C33)</f>
         <v>0</v>
       </c>
-      <c r="D34" s="51" t="s">
+      <c r="D34" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="50" t="n">
+      <c r="E34" s="49" t="n">
         <f aca="false">SUM(E28:E33)</f>
         <v>17</v>
       </c>
-      <c r="F34" s="51" t="s">
+      <c r="F34" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="G34" s="59" t="n">
+      <c r="G34" s="58" t="n">
         <f aca="false">SUM(G28:G33)</f>
         <v>0</v>
       </c>
-      <c r="H34" s="49" t="s">
+      <c r="H34" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="I34" s="50" t="n">
+      <c r="I34" s="49" t="n">
         <f aca="false">SUM(I28:I33)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="37"/>
+      <c r="J34" s="36"/>
       <c r="K34" s="13" t="s">
         <v>134</v>
       </c>
@@ -3946,15 +3956,15 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="69" t="s">
+      <c r="A35" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="B35" s="39"/>
-      <c r="C35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="G35" s="40"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="37"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="36"/>
       <c r="K35" s="13" t="s">
         <v>137</v>
       </c>
@@ -3968,14 +3978,14 @@
         <v>138</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="63"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="37"/>
+    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="62"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="36"/>
       <c r="K36" s="13" t="s">
         <v>139</v>
       </c>
@@ -3989,14 +3999,14 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="63"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="40"/>
-      <c r="E37" s="40"/>
-      <c r="G37" s="70"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="37"/>
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="62"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="G37" s="69"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="36"/>
       <c r="K37" s="13" t="s">
         <v>141</v>
       </c>
@@ -4010,14 +4020,14 @@
         <v>142</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="63"/>
-      <c r="B38" s="39"/>
-      <c r="C38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="G38" s="70"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="37"/>
+    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="62"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="G38" s="69"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="36"/>
       <c r="K38" s="13" t="s">
         <v>143</v>
       </c>
@@ -4031,15 +4041,15 @@
         <v>145</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="63"/>
-      <c r="B39" s="39"/>
-      <c r="C39" s="40"/>
-      <c r="E39" s="40"/>
-      <c r="G39" s="70"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="37"/>
-      <c r="K39" s="44" t="s">
+    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="62"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="G39" s="69"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="36"/>
+      <c r="K39" s="43" t="s">
         <v>27</v>
       </c>
       <c r="L39" s="14" t="n">
@@ -4052,15 +4062,15 @@
         <v>147</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="63"/>
-      <c r="B40" s="39"/>
-      <c r="C40" s="40"/>
-      <c r="E40" s="40"/>
-      <c r="G40" s="70"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="37"/>
-      <c r="K40" s="44" t="s">
+    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="62"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="G40" s="69"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="43" t="s">
         <v>148</v>
       </c>
       <c r="M40" s="13" t="s">
@@ -4070,253 +4080,253 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="58"/>
-      <c r="B41" s="49" t="s">
+    <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="57"/>
+      <c r="B41" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="50" t="n">
+      <c r="C41" s="49" t="n">
         <f aca="false">SUM(C35:C40)</f>
         <v>0</v>
       </c>
-      <c r="D41" s="51" t="s">
+      <c r="D41" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="E41" s="50" t="n">
+      <c r="E41" s="49" t="n">
         <f aca="false">SUM(E35:E40)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="51" t="s">
+      <c r="F41" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="G41" s="50" t="n">
+      <c r="G41" s="49" t="n">
         <f aca="false">SUM(G35:G40)</f>
         <v>0</v>
       </c>
-      <c r="H41" s="51" t="s">
+      <c r="H41" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="I41" s="50" t="n">
+      <c r="I41" s="49" t="n">
         <f aca="false">SUM(I35:I40)</f>
         <v>0</v>
       </c>
-      <c r="J41" s="37"/>
+      <c r="J41" s="36"/>
       <c r="K41" s="17"/>
     </row>
-    <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="71" t="s">
+    <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="70" t="s">
         <v>151</v>
       </c>
-      <c r="B42" s="72"/>
-      <c r="C42" s="64"/>
-      <c r="D42" s="72"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="64"/>
-      <c r="H42" s="72"/>
-      <c r="I42" s="64"/>
-      <c r="J42" s="73"/>
-      <c r="K42" s="66" t="s">
+      <c r="B42" s="71"/>
+      <c r="C42" s="63"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="65" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J43" s="73"/>
+    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J43" s="72"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="74" t="s">
+      <c r="A44" s="73" t="s">
         <v>153</v>
       </c>
-      <c r="B44" s="74"/>
-      <c r="C44" s="74"/>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="74"/>
-      <c r="H44" s="74"/>
-      <c r="I44" s="74"/>
-      <c r="J44" s="74"/>
+      <c r="B44" s="73"/>
+      <c r="C44" s="73"/>
+      <c r="D44" s="73"/>
+      <c r="E44" s="73"/>
+      <c r="F44" s="73"/>
+      <c r="G44" s="73"/>
+      <c r="H44" s="73"/>
+      <c r="I44" s="73"/>
+      <c r="J44" s="73"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="74"/>
-      <c r="B45" s="74"/>
-      <c r="C45" s="74"/>
-      <c r="D45" s="74"/>
-      <c r="E45" s="74"/>
-      <c r="F45" s="74"/>
-      <c r="G45" s="74"/>
-      <c r="H45" s="74"/>
-      <c r="I45" s="74"/>
-      <c r="J45" s="74"/>
+      <c r="A45" s="73"/>
+      <c r="B45" s="73"/>
+      <c r="C45" s="73"/>
+      <c r="D45" s="73"/>
+      <c r="E45" s="73"/>
+      <c r="F45" s="73"/>
+      <c r="G45" s="73"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="73"/>
+      <c r="J45" s="73"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="74"/>
-      <c r="B46" s="74"/>
-      <c r="C46" s="74"/>
-      <c r="D46" s="74"/>
-      <c r="E46" s="74"/>
-      <c r="F46" s="74"/>
-      <c r="G46" s="74"/>
-      <c r="H46" s="74"/>
-      <c r="I46" s="74"/>
-      <c r="J46" s="74"/>
+      <c r="A46" s="73"/>
+      <c r="B46" s="73"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="73"/>
+      <c r="F46" s="73"/>
+      <c r="G46" s="73"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="73"/>
+      <c r="J46" s="73"/>
       <c r="M46" s="17"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="74"/>
-      <c r="B47" s="74"/>
-      <c r="C47" s="74"/>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="74"/>
-      <c r="H47" s="74"/>
-      <c r="I47" s="74"/>
-      <c r="J47" s="74"/>
+      <c r="A47" s="73"/>
+      <c r="B47" s="73"/>
+      <c r="C47" s="73"/>
+      <c r="D47" s="73"/>
+      <c r="E47" s="73"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="73"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73"/>
+      <c r="J47" s="73"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="74"/>
-      <c r="B48" s="74"/>
-      <c r="C48" s="74"/>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="74"/>
-      <c r="H48" s="74"/>
-      <c r="I48" s="74"/>
-      <c r="J48" s="74"/>
+      <c r="A48" s="73"/>
+      <c r="B48" s="73"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="73"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="73"/>
+      <c r="I48" s="73"/>
+      <c r="J48" s="73"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="74"/>
-      <c r="B49" s="74"/>
-      <c r="C49" s="74"/>
-      <c r="D49" s="74"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="74"/>
-      <c r="H49" s="74"/>
-      <c r="I49" s="74"/>
-      <c r="J49" s="74"/>
+      <c r="A49" s="73"/>
+      <c r="B49" s="73"/>
+      <c r="C49" s="73"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="73"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73"/>
+      <c r="J49" s="73"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="74"/>
-      <c r="B50" s="74"/>
-      <c r="C50" s="74"/>
-      <c r="D50" s="74"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="74"/>
-      <c r="H50" s="74"/>
-      <c r="I50" s="74"/>
-      <c r="J50" s="74"/>
+      <c r="A50" s="73"/>
+      <c r="B50" s="73"/>
+      <c r="C50" s="73"/>
+      <c r="D50" s="73"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="73"/>
+      <c r="G50" s="73"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73"/>
+      <c r="J50" s="73"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="74"/>
-      <c r="B51" s="74"/>
-      <c r="C51" s="74"/>
-      <c r="D51" s="74"/>
-      <c r="E51" s="74"/>
-      <c r="F51" s="74"/>
-      <c r="G51" s="74"/>
-      <c r="H51" s="74"/>
-      <c r="I51" s="74"/>
-      <c r="J51" s="74"/>
+      <c r="A51" s="73"/>
+      <c r="B51" s="73"/>
+      <c r="C51" s="73"/>
+      <c r="D51" s="73"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="73"/>
+      <c r="G51" s="73"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73"/>
+      <c r="J51" s="73"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="74"/>
-      <c r="B52" s="74"/>
-      <c r="C52" s="74"/>
-      <c r="D52" s="74"/>
-      <c r="E52" s="74"/>
-      <c r="F52" s="74"/>
-      <c r="G52" s="74"/>
-      <c r="H52" s="74"/>
-      <c r="I52" s="74"/>
-      <c r="J52" s="74"/>
+      <c r="A52" s="73"/>
+      <c r="B52" s="73"/>
+      <c r="C52" s="73"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="73"/>
+      <c r="G52" s="73"/>
+      <c r="H52" s="73"/>
+      <c r="I52" s="73"/>
+      <c r="J52" s="73"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="74"/>
-      <c r="B53" s="74"/>
-      <c r="C53" s="74"/>
-      <c r="D53" s="74"/>
-      <c r="E53" s="74"/>
-      <c r="F53" s="74"/>
-      <c r="G53" s="74"/>
-      <c r="H53" s="74"/>
-      <c r="I53" s="74"/>
-      <c r="J53" s="74"/>
+      <c r="A53" s="73"/>
+      <c r="B53" s="73"/>
+      <c r="C53" s="73"/>
+      <c r="D53" s="73"/>
+      <c r="E53" s="73"/>
+      <c r="F53" s="73"/>
+      <c r="G53" s="73"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73"/>
+      <c r="J53" s="73"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="74"/>
-      <c r="B54" s="74"/>
-      <c r="C54" s="74"/>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="74"/>
-      <c r="H54" s="74"/>
-      <c r="I54" s="74"/>
-      <c r="J54" s="74"/>
+      <c r="A54" s="73"/>
+      <c r="B54" s="73"/>
+      <c r="C54" s="73"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="73"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73"/>
+      <c r="J54" s="73"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="74"/>
-      <c r="B55" s="74"/>
-      <c r="C55" s="74"/>
-      <c r="D55" s="74"/>
-      <c r="E55" s="74"/>
-      <c r="F55" s="74"/>
-      <c r="G55" s="74"/>
-      <c r="H55" s="74"/>
-      <c r="I55" s="74"/>
-      <c r="J55" s="74"/>
+      <c r="A55" s="73"/>
+      <c r="B55" s="73"/>
+      <c r="C55" s="73"/>
+      <c r="D55" s="73"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="73"/>
+      <c r="G55" s="73"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73"/>
+      <c r="J55" s="73"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="74"/>
-      <c r="B56" s="74"/>
-      <c r="C56" s="74"/>
-      <c r="D56" s="74"/>
-      <c r="E56" s="74"/>
-      <c r="F56" s="74"/>
-      <c r="G56" s="74"/>
-      <c r="H56" s="74"/>
-      <c r="I56" s="74"/>
-      <c r="J56" s="74"/>
+      <c r="A56" s="73"/>
+      <c r="B56" s="73"/>
+      <c r="C56" s="73"/>
+      <c r="D56" s="73"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="73"/>
+      <c r="G56" s="73"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73"/>
+      <c r="J56" s="73"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="74"/>
-      <c r="B57" s="74"/>
-      <c r="C57" s="74"/>
-      <c r="D57" s="74"/>
-      <c r="E57" s="74"/>
-      <c r="F57" s="74"/>
-      <c r="G57" s="74"/>
-      <c r="H57" s="74"/>
-      <c r="I57" s="74"/>
-      <c r="J57" s="74"/>
+      <c r="A57" s="73"/>
+      <c r="B57" s="73"/>
+      <c r="C57" s="73"/>
+      <c r="D57" s="73"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="73"/>
+      <c r="G57" s="73"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73"/>
+      <c r="J57" s="73"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="74"/>
-      <c r="B58" s="74"/>
-      <c r="C58" s="74"/>
-      <c r="D58" s="74"/>
-      <c r="E58" s="74"/>
-      <c r="F58" s="74"/>
-      <c r="G58" s="74"/>
-      <c r="H58" s="74"/>
-      <c r="I58" s="74"/>
-      <c r="J58" s="74"/>
+      <c r="A58" s="73"/>
+      <c r="B58" s="73"/>
+      <c r="C58" s="73"/>
+      <c r="D58" s="73"/>
+      <c r="E58" s="73"/>
+      <c r="F58" s="73"/>
+      <c r="G58" s="73"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73"/>
+      <c r="J58" s="73"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="74"/>
-      <c r="B59" s="74"/>
-      <c r="C59" s="74"/>
-      <c r="D59" s="74"/>
-      <c r="E59" s="74"/>
-      <c r="F59" s="74"/>
-      <c r="G59" s="74"/>
-      <c r="H59" s="74"/>
-      <c r="I59" s="74"/>
-      <c r="J59" s="74"/>
+      <c r="A59" s="73"/>
+      <c r="B59" s="73"/>
+      <c r="C59" s="73"/>
+      <c r="D59" s="73"/>
+      <c r="E59" s="73"/>
+      <c r="F59" s="73"/>
+      <c r="G59" s="73"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73"/>
+      <c r="J59" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="3">
